--- a/开发学习规划/开发学习规划2017年10月18日.xlsx
+++ b/开发学习规划/开发学习规划2017年10月18日.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="20910"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="2280" windowWidth="25600" windowHeight="15540" tabRatio="500"/>
+    <workbookView xWindow="-22360" yWindow="1600" windowWidth="25360" windowHeight="15360" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -19,16 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BeginTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EndTime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -57,7 +53,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>记录时间</t>
+    <t>计划时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实施时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、蚂蚁推推（推推1-生产）磁盘扩容；2、蚁聚智能 SLB新增实例；3、赛门铁克iOS支持证书SLB里配置；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、2017/10/24，AM:00：00-01：30；2、AM&amp;PM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -65,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -81,6 +89,32 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -91,7 +125,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -120,19 +154,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="超链接" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="访问过的超链接" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="普通" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -465,134 +503,142 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="28" customHeight="1" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="2"/>
-    <col min="2" max="2" width="25.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10.83203125" style="2"/>
-    <col min="6" max="6" width="24.1640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="50.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="1"/>
+    <col min="6" max="6" width="24.1640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="28" customHeight="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28" customHeight="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28" customHeight="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28" customHeight="1">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="28" customHeight="1">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="28" customHeight="1">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28" customHeight="1">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
+    <row r="8" spans="1:7" ht="28" customHeight="1">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="28" customHeight="1">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="28" customHeight="1">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28" customHeight="1">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28" customHeight="1">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="28" customHeight="1">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28" customHeight="1">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28" customHeight="1">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28" customHeight="1">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-    </row>
     <row r="10" spans="1:7" ht="28" customHeight="1">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28" customHeight="1">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28" customHeight="1">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28" customHeight="1">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28" customHeight="1">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28" customHeight="1">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28" customHeight="1">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="28" customHeight="1">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="28" customHeight="1">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
